--- a/YRIGOYEN 9730/Septiembre/YRIGOYEN7630-Septiembre.xlsx
+++ b/YRIGOYEN 9730/Septiembre/YRIGOYEN7630-Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\YRIGOYEN 9730\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E06E4A5-86E9-4813-B3C4-27B96EBB15C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81FA899B-4E6E-4302-BCCF-B3A1672B5091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$121</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$123</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="116">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -311,9 +311,6 @@
     <t>AGREGAR A LA CADENA</t>
   </si>
   <si>
-    <t>Sra Fernanda Reemplazo por vacaciones</t>
-  </si>
-  <si>
     <t>Gastos bancarios</t>
   </si>
   <si>
@@ -323,24 +320,6 @@
     <t>Honorarios administracion</t>
   </si>
   <si>
-    <t>VTO 15/09</t>
-  </si>
-  <si>
-    <t>Debito 12/08</t>
-  </si>
-  <si>
-    <t>PERÍODO: AGOSTO</t>
-  </si>
-  <si>
-    <t>Sindicatos mes de AGOSTO</t>
-  </si>
-  <si>
-    <t>Gustavo padron - Sr contador honorarios JULIO y AGOSTO</t>
-  </si>
-  <si>
-    <t>Megasec - compra de bastago de polvo y manometro</t>
-  </si>
-  <si>
     <t>Transf 26/08</t>
   </si>
   <si>
@@ -353,28 +332,49 @@
     <t>Federacion patronal  Seguro obligatorio de consorcio</t>
   </si>
   <si>
-    <t>Debito 07/08</t>
-  </si>
-  <si>
-    <t>Debito 18/08</t>
-  </si>
-  <si>
-    <t>Ascensores lema - Mantenimiento Julio</t>
-  </si>
-  <si>
-    <t>Transf 29/08</t>
-  </si>
-  <si>
     <t>PENDIENTE PASAR COSAS DE DOARTERO ARREGLO DPTO AGUSTIN</t>
   </si>
   <si>
-    <t>Debito 03/08</t>
-  </si>
-  <si>
-    <t>Debito 04/08</t>
-  </si>
-  <si>
-    <t>Debito 02/08</t>
+    <t>VTO 15/10</t>
+  </si>
+  <si>
+    <t>PERÍODO: SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Sindicatos mes de SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Ascensores lema - Mantenimiento agosto</t>
+  </si>
+  <si>
+    <t>Transf 11/09</t>
+  </si>
+  <si>
+    <t>Gustavo padron - Sr contador honorarios SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fumigacion </t>
+  </si>
+  <si>
+    <t>Debito 08/09</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>Debito 12/09</t>
+  </si>
+  <si>
+    <t>Debito 16/09</t>
+  </si>
+  <si>
+    <t>Debito 04/09</t>
+  </si>
+  <si>
+    <t>Doartero Julio  - Cambio de cañeria interna del baño completa y ramal cloacal (Dpto. 10)</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -382,14 +382,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0.0_-;\-&quot;$&quot;\ * #,##0.0_-;_-&quot;$&quot;\ * &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="29" x14ac:knownFonts="1">
     <font>
@@ -1088,8 +1088,8 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="212">
@@ -1100,7 +1100,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="8" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1115,9 +1115,9 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1132,7 +1132,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1142,40 +1142,40 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="15" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1189,7 +1189,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1197,98 +1197,98 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="4" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="6" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="8" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="23" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="4" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="8" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="10" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="16" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="11" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1296,65 +1296,68 @@
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="6" fillId="4" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="6" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="25" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="26" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="26" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="8" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="44" fontId="27" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="3"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1380,10 +1383,19 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1401,12 +1413,6 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1422,14 +1428,8 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1796,7 +1796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M125"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -1831,12 +1831,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16"/>
-      <c r="B3" s="191" t="s">
+      <c r="B3" s="192" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="191"/>
-      <c r="D3" s="191"/>
-      <c r="E3" s="192"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="193"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
@@ -1854,7 +1854,7 @@
         <v>60</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="73" t="s">
@@ -1874,49 +1874,49 @@
       <c r="E6" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="194" t="s">
-        <v>98</v>
-      </c>
-      <c r="C8" s="194"/>
+      <c r="B8" s="195" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="195"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="194"/>
-      <c r="C9" s="194"/>
+      <c r="B9" s="195"/>
+      <c r="C9" s="195"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="194"/>
-      <c r="C10" s="194"/>
+      <c r="B10" s="195"/>
+      <c r="C10" s="195"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="193" t="s">
+      <c r="A13" s="194" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="193"/>
-      <c r="C13" s="193"/>
-      <c r="D13" s="193"/>
-      <c r="E13" s="193"/>
+      <c r="B13" s="194"/>
+      <c r="C13" s="194"/>
+      <c r="D13" s="194"/>
+      <c r="E13" s="194"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="193"/>
-      <c r="B14" s="193"/>
-      <c r="C14" s="193"/>
-      <c r="D14" s="193"/>
-      <c r="E14" s="193"/>
+      <c r="A14" s="194"/>
+      <c r="B14" s="194"/>
+      <c r="C14" s="194"/>
+      <c r="D14" s="194"/>
+      <c r="E14" s="194"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="193"/>
-      <c r="B15" s="193"/>
-      <c r="C15" s="193"/>
-      <c r="D15" s="193"/>
-      <c r="E15" s="193"/>
+      <c r="A15" s="194"/>
+      <c r="B15" s="194"/>
+      <c r="C15" s="194"/>
+      <c r="D15" s="194"/>
+      <c r="E15" s="194"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="193"/>
-      <c r="B16" s="193"/>
-      <c r="C16" s="193"/>
-      <c r="D16" s="193"/>
-      <c r="E16" s="193"/>
+      <c r="A16" s="194"/>
+      <c r="B16" s="194"/>
+      <c r="C16" s="194"/>
+      <c r="D16" s="194"/>
+      <c r="E16" s="194"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
@@ -1948,7 +1948,7 @@
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
       <c r="D22" s="160">
-        <v>773598</v>
+        <v>748673</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -1959,7 +1959,7 @@
       <c r="D23" s="160"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="59" t="s">
         <v>36</v>
       </c>
@@ -1967,7 +1967,7 @@
       <c r="C24" s="59"/>
       <c r="D24" s="169">
         <f>SUM(D22:D23)</f>
-        <v>773598</v>
+        <v>748673</v>
       </c>
       <c r="E24" s="144"/>
       <c r="G24" s="22"/>
@@ -2031,18 +2031,14 @@
       </c>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>94</v>
-      </c>
+    <row r="32" spans="1:7" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="170">
-        <v>28000</v>
-      </c>
+      <c r="D32" s="170"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="59" t="s">
         <v>36</v>
       </c>
@@ -2050,7 +2046,7 @@
       <c r="C33" s="59"/>
       <c r="D33" s="171">
         <f>SUM(D25:D32)</f>
-        <v>28000</v>
+        <v>0</v>
       </c>
       <c r="E33" s="144"/>
     </row>
@@ -2063,7 +2059,7 @@
       <c r="D34" s="172"/>
       <c r="E34" s="145">
         <f>D24+D33</f>
-        <v>801598</v>
+        <v>748673</v>
       </c>
       <c r="F34" s="22"/>
     </row>
@@ -2077,29 +2073,29 @@
       <c r="E35" s="146"/>
     </row>
     <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="189" t="s">
-        <v>102</v>
-      </c>
-      <c r="B36" s="190"/>
+      <c r="A36" s="190" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="191"/>
       <c r="C36" s="54"/>
       <c r="D36" s="160">
-        <f>2*30000</f>
-        <v>60000</v>
+        <f>30000</f>
+        <v>30000</v>
       </c>
       <c r="E36" s="147"/>
     </row>
     <row r="37" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="189" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="190"/>
+      <c r="A37" s="190" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="191"/>
       <c r="C37" s="54"/>
       <c r="D37" s="174">
         <v>112400</v>
       </c>
       <c r="E37" s="147"/>
       <c r="H37" s="158" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2111,7 +2107,7 @@
       <c r="D38" s="175"/>
       <c r="E38" s="148">
         <f>SUM(D36:D37)</f>
-        <v>172400</v>
+        <v>142400</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -2124,30 +2120,30 @@
       <c r="E39" s="149"/>
     </row>
     <row r="40" spans="1:8" s="39" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="187" t="s">
-        <v>106</v>
-      </c>
-      <c r="B40" s="188"/>
+      <c r="A40" s="188" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="189"/>
       <c r="C40" s="56"/>
       <c r="D40" s="177">
         <v>26570</v>
       </c>
       <c r="E40" s="161" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="187" t="s">
-        <v>107</v>
-      </c>
-      <c r="B41" s="188"/>
+      <c r="A41" s="188" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="189"/>
       <c r="C41" s="56"/>
       <c r="D41" s="178">
         <v>54278</v>
       </c>
       <c r="E41" s="150" t="str">
         <f>E40</f>
-        <v>Debito 04/08</v>
+        <v>Debito 04/09</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2178,10 +2174,10 @@
       <c r="B44" s="5"/>
       <c r="C44" s="54"/>
       <c r="D44" s="180">
-        <v>621996.29</v>
+        <v>562727.52</v>
       </c>
       <c r="E44" s="161" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="G44" s="127"/>
     </row>
@@ -2195,7 +2191,7 @@
         <v>10602.27</v>
       </c>
       <c r="E45" s="161" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -2209,51 +2205,51 @@
       </c>
       <c r="E46" s="161" t="str">
         <f>E45</f>
-        <v>Debito 18/08</v>
+        <v>Debito 16/09</v>
       </c>
       <c r="G46" s="143"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="164">
-        <v>86171.08</v>
+        <v>79308.399999999994</v>
       </c>
       <c r="E47" s="161" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="str">
         <f>A47</f>
-        <v>Sindicatos mes de AGOSTO</v>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="164">
-        <v>5681.31</v>
+        <v>5140.8</v>
       </c>
       <c r="E48" s="162" t="str">
         <f>E47</f>
-        <v>Debito 12/08</v>
+        <v>Debito 12/09</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="str">
         <f>A48</f>
-        <v>Sindicatos mes de AGOSTO</v>
+        <v>Sindicatos mes de SEPTIEMBRE</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="164">
-        <v>51131.82</v>
+        <v>46261.66</v>
       </c>
       <c r="E49" s="163" t="str">
         <f>E48</f>
-        <v>Debito 12/08</v>
+        <v>Debito 12/09</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2265,7 +2261,7 @@
       <c r="D50" s="181"/>
       <c r="E50" s="151">
         <f>SUM(D44:D49)</f>
-        <v>851115.06</v>
+        <v>779572.94000000018</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -2284,10 +2280,10 @@
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="164">
-        <v>52825.87</v>
+        <v>48142.59</v>
       </c>
       <c r="E52" s="161" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2297,9 +2293,9 @@
       <c r="B53" s="164"/>
       <c r="C53" s="5"/>
       <c r="D53" s="164">
-        <v>23726.77</v>
-      </c>
-      <c r="E53" s="161" t="s">
+        <v>0</v>
+      </c>
+      <c r="E53" s="211" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2310,568 +2306,598 @@
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="164">
-        <v>27113.49</v>
+        <v>26472.2</v>
       </c>
       <c r="E54" s="161" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="187" t="s">
+      <c r="A55" s="188" t="s">
         <v>80</v>
       </c>
-      <c r="B55" s="188"/>
+      <c r="B55" s="189"/>
       <c r="C55" s="5"/>
       <c r="D55" s="164">
-        <v>355815.42</v>
-      </c>
-      <c r="E55" s="161" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="30" t="s">
+        <v>303116.46999999997</v>
+      </c>
+      <c r="E55" s="165" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="188" t="s">
+        <v>80</v>
+      </c>
+      <c r="B56" s="189"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="164">
+        <v>309335.53999999998</v>
+      </c>
+      <c r="E56" s="165" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="182"/>
-      <c r="E56" s="151">
-        <f>SUM(D52:D55)</f>
-        <v>459481.55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="36"/>
       <c r="B57" s="30"/>
       <c r="C57" s="30"/>
-      <c r="D57" s="175"/>
-      <c r="E57" s="154"/>
-    </row>
-    <row r="58" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="166" t="s">
-        <v>110</v>
-      </c>
-      <c r="B58" s="159"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="164">
-        <v>54500</v>
-      </c>
-      <c r="E58" s="165" t="s">
-        <v>111</v>
-      </c>
+      <c r="D57" s="182"/>
+      <c r="E57" s="151">
+        <f>SUM(D52:D56)</f>
+        <v>687066.79999999993</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="36"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="175"/>
+      <c r="E58" s="154"/>
     </row>
     <row r="59" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="189" t="s">
-        <v>103</v>
-      </c>
-      <c r="B59" s="190"/>
+      <c r="A59" s="166" t="s">
+        <v>105</v>
+      </c>
+      <c r="B59" s="159"/>
       <c r="C59" s="5"/>
       <c r="D59" s="164">
-        <v>34000</v>
+        <v>71200</v>
       </c>
       <c r="E59" s="165" t="s">
-        <v>104</v>
-      </c>
-      <c r="H59" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="187"/>
-      <c r="B60" s="188"/>
+      <c r="A60" s="166" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="159"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="109"/>
-      <c r="E60" s="186"/>
-      <c r="I60" s="187"/>
-      <c r="J60" s="188"/>
-    </row>
-    <row r="61" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="30" t="s">
+      <c r="D60" s="164">
+        <v>65500</v>
+      </c>
+      <c r="E60" s="165" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="190" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="191"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="164">
+        <v>1050000</v>
+      </c>
+      <c r="E61" s="165" t="s">
+        <v>97</v>
+      </c>
+      <c r="H61" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="188" t="s">
+        <v>108</v>
+      </c>
+      <c r="B62" s="189"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="109">
+        <v>40000</v>
+      </c>
+      <c r="E62" s="165" t="s">
+        <v>106</v>
+      </c>
+      <c r="I62" s="188"/>
+      <c r="J62" s="189"/>
+    </row>
+    <row r="63" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="35"/>
-      <c r="E61" s="155">
-        <f>SUM(D58:D60)</f>
-        <v>88500</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="36" t="s">
+      <c r="B63" s="36"/>
+      <c r="C63" s="36"/>
+      <c r="D63" s="35"/>
+      <c r="E63" s="155">
+        <f>SUM(D59:D62)</f>
+        <v>1226700</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B62" s="69"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="172"/>
-      <c r="E62" s="154"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="164">
+      <c r="B64" s="69"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="172"/>
+      <c r="E64" s="154"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="164">
         <v>53000</v>
       </c>
-      <c r="E63" s="156"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="164">
-        <v>46522.14</v>
-      </c>
-      <c r="E64" s="41"/>
-    </row>
-    <row r="65" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="53" t="s">
-        <v>16</v>
-      </c>
-      <c r="B65" s="53"/>
-      <c r="C65" s="53"/>
-      <c r="D65" s="112"/>
-      <c r="E65" s="106">
-        <f>SUM(D63:D64)</f>
-        <v>99522.14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="5"/>
+      <c r="E65" s="156"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
-      <c r="D66" s="105"/>
-      <c r="E66" s="113"/>
+      <c r="D66" s="164">
+        <v>56008.43</v>
+      </c>
+      <c r="E66" s="41"/>
     </row>
     <row r="67" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="31" t="s">
+      <c r="A67" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67" s="53"/>
+      <c r="C67" s="53"/>
+      <c r="D67" s="112"/>
+      <c r="E67" s="106">
+        <f>SUM(D65:D66)</f>
+        <v>109008.43</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="105"/>
+      <c r="E68" s="113"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B67" s="31"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="114"/>
-      <c r="E67" s="115">
-        <f>3500000-2553464.75</f>
-        <v>946535.25</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1"/>
-      <c r="D68" s="116"/>
-      <c r="E68" s="117"/>
-      <c r="F68" s="45"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="3" t="s">
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="114"/>
+      <c r="E69" s="115"/>
+    </row>
+    <row r="70" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="1"/>
+      <c r="D70" s="116"/>
+      <c r="E70" s="117"/>
+      <c r="F70" s="45"/>
+    </row>
+    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B69" s="10"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="118"/>
-      <c r="E69" s="119">
-        <f>(SUM(E27:E67))</f>
-        <v>3500000</v>
-      </c>
-      <c r="F69" s="143"/>
-      <c r="G69" s="45"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D70" s="116"/>
-      <c r="E70" s="116"/>
-    </row>
-    <row r="71" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="116"/>
-      <c r="E71" s="116"/>
-      <c r="H71" s="183"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="118"/>
+      <c r="E71" s="119">
+        <f>(SUM(E27:E69))</f>
+        <v>3774269.1700000004</v>
+      </c>
+      <c r="F71" s="143"/>
+      <c r="G71" s="45"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="11" t="s">
+      <c r="D72" s="116"/>
+      <c r="E72" s="116"/>
+    </row>
+    <row r="73" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="116"/>
+      <c r="E73" s="116"/>
+      <c r="H73" s="183"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="B72" s="12"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="120"/>
-      <c r="E72" s="121"/>
-    </row>
-    <row r="73" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="187"/>
-      <c r="B73" s="188"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="131"/>
-      <c r="E73" s="107"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="187"/>
-      <c r="B74" s="188"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="109"/>
-      <c r="E74" s="107"/>
-    </row>
-    <row r="75" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="189"/>
-      <c r="B75" s="190"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="120"/>
+      <c r="E74" s="121"/>
+    </row>
+    <row r="75" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="188"/>
+      <c r="B75" s="189"/>
       <c r="C75" s="5"/>
-      <c r="D75" s="109"/>
+      <c r="D75" s="131"/>
       <c r="E75" s="107"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="108"/>
-      <c r="B76" s="110"/>
+      <c r="A76" s="188"/>
+      <c r="B76" s="189"/>
       <c r="C76" s="5"/>
       <c r="D76" s="109"/>
       <c r="E76" s="107"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="51"/>
-      <c r="B77" s="50"/>
-      <c r="C77" s="50"/>
-      <c r="D77" s="60"/>
-      <c r="E77" s="60">
-        <f>SUM(D73:D76)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="80" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="31" t="s">
+    <row r="77" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="190"/>
+      <c r="B77" s="191"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="109"/>
+      <c r="E77" s="107"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="108"/>
+      <c r="B78" s="110"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="109"/>
+      <c r="E78" s="107"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="51"/>
+      <c r="B79" s="50"/>
+      <c r="C79" s="50"/>
+      <c r="D79" s="60"/>
+      <c r="E79" s="60">
+        <f>SUM(D75:D78)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B80" s="31"/>
-      <c r="C80" s="31"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="104"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B82" s="10"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="70">
-        <f>E77+E80</f>
-        <v>0</v>
-      </c>
+      <c r="B82" s="31"/>
+      <c r="C82" s="31"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="104"/>
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="102" t="s">
-        <v>14</v>
-      </c>
-      <c r="B84" s="103">
-        <f>E69</f>
-        <v>3500000</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" s="103">
-        <f>E69-E67</f>
-        <v>2553464.75</v>
-      </c>
-    </row>
+      <c r="A84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" s="10"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="70">
+        <f>E79+E82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="102" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B86" s="103">
-        <f>E82-E80</f>
-        <v>0</v>
+        <f>E71</f>
+        <v>3774269.1700000004</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" s="103">
+        <f>E71-E69</f>
+        <v>3774269.1700000004</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="102" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="103">
+        <f>E84-E82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="B87" s="103">
-        <f>E82</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="195"/>
-      <c r="B90" s="195"/>
-      <c r="C90" s="195"/>
-      <c r="D90" s="195"/>
-      <c r="E90" s="195"/>
-    </row>
-    <row r="91" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="195"/>
-      <c r="B91" s="195"/>
-      <c r="C91" s="195"/>
-      <c r="D91" s="195"/>
-      <c r="E91" s="195"/>
-    </row>
-    <row r="92" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="195"/>
-      <c r="B92" s="195"/>
-      <c r="C92" s="195"/>
-      <c r="D92" s="195"/>
-      <c r="E92" s="195"/>
-    </row>
-    <row r="94" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="23" t="s">
+      <c r="B89" s="103">
+        <f>E84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="186"/>
+      <c r="B92" s="186"/>
+      <c r="C92" s="186"/>
+      <c r="D92" s="186"/>
+      <c r="E92" s="186"/>
+    </row>
+    <row r="93" spans="1:5" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="186"/>
+      <c r="B93" s="186"/>
+      <c r="C93" s="186"/>
+      <c r="D93" s="186"/>
+      <c r="E93" s="186"/>
+    </row>
+    <row r="94" spans="1:5" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="186"/>
+      <c r="B94" s="186"/>
+      <c r="C94" s="186"/>
+      <c r="D94" s="186"/>
+      <c r="E94" s="186"/>
+    </row>
+    <row r="96" spans="1:5" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="B94" s="128"/>
-      <c r="C94" s="24"/>
-    </row>
-    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="34"/>
-      <c r="B95" s="61">
-        <v>0</v>
-      </c>
-      <c r="C95" s="26"/>
-    </row>
-    <row r="96" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="25" t="s">
+      <c r="B96" s="128"/>
+      <c r="C96" s="24"/>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="34"/>
+      <c r="B97" s="61">
+        <v>0</v>
+      </c>
+      <c r="C97" s="26"/>
+    </row>
+    <row r="98" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B96" s="41">
+      <c r="B98" s="41">
         <f>PRORRATEO!F29</f>
-        <v>3065070.3000000007</v>
-      </c>
-      <c r="C96" s="24"/>
-    </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="25"/>
-      <c r="B97" s="41">
-        <v>0</v>
-      </c>
-      <c r="C97" s="24"/>
-    </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="25" t="s">
+        <v>2888514.2500000005</v>
+      </c>
+      <c r="C98" s="24"/>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="25"/>
+      <c r="B99" s="41">
+        <v>0</v>
+      </c>
+      <c r="C99" s="24"/>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="B98" s="111">
-        <f>B120</f>
-        <v>0</v>
-      </c>
-      <c r="C98" s="24"/>
-    </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="28"/>
-      <c r="B99" s="49"/>
-      <c r="C99" s="24"/>
-    </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="126" t="s">
+      <c r="B100" s="111">
+        <f>B122</f>
+        <v>0</v>
+      </c>
+      <c r="C100" s="24"/>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="28"/>
+      <c r="B101" s="49"/>
+      <c r="C101" s="24"/>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="B100" s="49"/>
-      <c r="C100" s="24"/>
-    </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="40" t="s">
+      <c r="B102" s="49"/>
+      <c r="C102" s="24"/>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B101" s="49">
-        <f>-B85</f>
-        <v>-2553464.75</v>
-      </c>
-      <c r="C101" s="24"/>
-    </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="28" t="s">
+      <c r="B103" s="49">
+        <f>-B87</f>
+        <v>-3774269.1700000004</v>
+      </c>
+      <c r="C103" s="24"/>
+    </row>
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B102" s="49">
-        <f>-(B86)</f>
-        <v>0</v>
-      </c>
-      <c r="C102" s="24"/>
-    </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="33" t="s">
+      <c r="B104" s="49">
+        <f>-(B88)</f>
+        <v>0</v>
+      </c>
+      <c r="C104" s="24"/>
+    </row>
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="B103" s="61">
-        <f>SUM(B95:B102)</f>
-        <v>511605.55000000075</v>
-      </c>
-      <c r="C103" s="27"/>
-      <c r="D103" s="45"/>
-    </row>
-    <row r="104" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="42"/>
-      <c r="C104" s="27"/>
-      <c r="D104" s="45"/>
-      <c r="E104" s="129"/>
-      <c r="F104" s="130"/>
-    </row>
-    <row r="105" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="43"/>
+      <c r="B105" s="61">
+        <f>SUM(B97:B104)</f>
+        <v>-885754.91999999993</v>
+      </c>
       <c r="C105" s="27"/>
-    </row>
-    <row r="106" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106"/>
+      <c r="D105" s="45"/>
+    </row>
+    <row r="106" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B106" s="42"/>
-      <c r="C106" s="38"/>
-    </row>
-    <row r="107" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="134" t="s">
+      <c r="C106" s="27"/>
+      <c r="D106" s="45"/>
+      <c r="E106" s="129"/>
+      <c r="F106" s="130"/>
+    </row>
+    <row r="107" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="43"/>
+      <c r="C107" s="27"/>
+    </row>
+    <row r="108" spans="1:6" s="39" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108"/>
+      <c r="B108" s="42"/>
+      <c r="C108" s="38"/>
+    </row>
+    <row r="109" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="134" t="s">
         <v>91</v>
       </c>
-      <c r="B107" s="135">
-        <v>-726690.58609999763</v>
-      </c>
-      <c r="C107" s="38"/>
-      <c r="D107" s="48"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A108" s="56" t="s">
-        <v>54</v>
-      </c>
-      <c r="B108" s="140">
-        <f>-B85</f>
-        <v>-2553464.75</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A109" s="56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B109" s="140">
-        <f>-B86</f>
-        <v>0</v>
-      </c>
+      <c r="B109" s="135">
+        <v>-215085.03609999688</v>
+      </c>
+      <c r="C109" s="38"/>
+      <c r="D109" s="48"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="56" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="B110" s="140">
-        <f>B120</f>
-        <v>0</v>
+        <f>-B87</f>
+        <v>-3774269.1700000004</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B111" s="140">
+        <f>-B88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="B112" s="140">
+        <f>B122</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="B111" s="141">
+      <c r="B113" s="141">
         <f>PRORRATEO!F29</f>
-        <v>3065070.3000000007</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A112" s="142" t="s">
+        <v>2888514.2500000005</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="B112" s="184"/>
-    </row>
-    <row r="113" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="138" t="s">
+      <c r="B114" s="184"/>
+    </row>
+    <row r="115" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="138" t="s">
         <v>51</v>
       </c>
-      <c r="B113" s="139">
-        <f>SUM(B107:C112)</f>
-        <v>-215085.03609999688</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="136"/>
-      <c r="B114" s="136"/>
-    </row>
-    <row r="115" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B115" s="139">
+        <f>SUM(B109:C114)</f>
+        <v>-1100839.9560999968</v>
+      </c>
+    </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="196" t="s">
+      <c r="A116" s="136"/>
+      <c r="B116" s="136"/>
+    </row>
+    <row r="117" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="187" t="s">
         <v>33</v>
       </c>
-      <c r="B116" s="196"/>
-      <c r="C116" s="196"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A117" s="196"/>
-      <c r="B117" s="196"/>
-      <c r="C117" s="196"/>
-    </row>
-    <row r="118" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="123"/>
-      <c r="B118" s="37"/>
-      <c r="C118" s="37">
+      <c r="B118" s="187"/>
+      <c r="C118" s="187"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="187"/>
+      <c r="B119" s="187"/>
+      <c r="C119" s="187"/>
+    </row>
+    <row r="120" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="123"/>
+      <c r="B120" s="37"/>
+      <c r="C120" s="37">
         <v>40000</v>
       </c>
-      <c r="E118" s="143"/>
-    </row>
-    <row r="119" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="123"/>
-      <c r="B119" s="125"/>
-      <c r="C119" s="122"/>
-      <c r="D119" s="143"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="46" t="s">
+      <c r="E120" s="143"/>
+    </row>
+    <row r="121" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="123"/>
+      <c r="B121" s="125"/>
+      <c r="C121" s="122"/>
+      <c r="D121" s="143"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B120" s="124">
-        <f>SUM(B118:B119)</f>
-        <v>0</v>
-      </c>
-      <c r="C120" s="47"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M121" s="8"/>
-    </row>
-    <row r="122" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="195"/>
-      <c r="B122" s="195"/>
-      <c r="C122" s="195"/>
-      <c r="D122" s="195"/>
-      <c r="E122" s="195"/>
+      <c r="B122" s="124">
+        <f>SUM(B120:B121)</f>
+        <v>0</v>
+      </c>
+      <c r="C122" s="47"/>
     </row>
     <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="195"/>
-      <c r="B123" s="195"/>
-      <c r="C123" s="195"/>
-      <c r="D123" s="195"/>
-      <c r="E123" s="195"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A124" s="195"/>
-      <c r="B124" s="195"/>
-      <c r="C124" s="195"/>
-      <c r="D124" s="195"/>
-      <c r="E124" s="195"/>
+      <c r="M123" s="8"/>
+    </row>
+    <row r="124" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="186"/>
+      <c r="B124" s="186"/>
+      <c r="C124" s="186"/>
+      <c r="D124" s="186"/>
+      <c r="E124" s="186"/>
     </row>
     <row r="125" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A125" s="195"/>
-      <c r="B125" s="195"/>
-      <c r="C125" s="195"/>
-      <c r="D125" s="195"/>
-      <c r="E125" s="195"/>
+      <c r="A125" s="186"/>
+      <c r="B125" s="186"/>
+      <c r="C125" s="186"/>
+      <c r="D125" s="186"/>
+      <c r="E125" s="186"/>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="186"/>
+      <c r="B126" s="186"/>
+      <c r="C126" s="186"/>
+      <c r="D126" s="186"/>
+      <c r="E126" s="186"/>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="186"/>
+      <c r="B127" s="186"/>
+      <c r="C127" s="186"/>
+      <c r="D127" s="186"/>
+      <c r="E127" s="186"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A122:E125"/>
-    <mergeCell ref="A116:C117"/>
-    <mergeCell ref="A90:E92"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A55:B55"/>
+  <mergeCells count="18">
+    <mergeCell ref="A56:B56"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="I62:J62"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A62:B62"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A124:E127"/>
+    <mergeCell ref="A118:C119"/>
+    <mergeCell ref="A92:E94"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A77:B77"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2907,15 +2933,15 @@
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
+      <c r="D1" s="201"/>
+      <c r="E1" s="201"/>
+      <c r="F1" s="201"/>
+      <c r="G1" s="201"/>
+      <c r="H1" s="201"/>
+      <c r="I1" s="201"/>
+      <c r="J1" s="201"/>
+      <c r="K1" s="201"/>
+      <c r="L1" s="201"/>
       <c r="M1" s="6"/>
       <c r="N1" s="6"/>
     </row>
@@ -2938,7 +2964,7 @@
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="133">
-        <v>3500000</v>
+        <v>3774269.1700000004</v>
       </c>
       <c r="M2" s="57"/>
       <c r="N2" s="57"/>
@@ -2961,68 +2987,68 @@
       <c r="N3" s="62"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="202" t="s">
+      <c r="A4" s="198" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="202" t="s">
+      <c r="B4" s="198" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="202" t="s">
+      <c r="C4" s="198" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="202" t="s">
+      <c r="D4" s="198" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="198" t="s">
+      <c r="E4" s="202" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="202" t="s">
+      <c r="F4" s="198" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="204" t="s">
+      <c r="G4" s="206" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="198" t="s">
+      <c r="H4" s="202" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="198" t="s">
+      <c r="I4" s="202" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="198" t="s">
+      <c r="J4" s="202" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="207" t="s">
+      <c r="K4" s="209" t="s">
         <v>86</v>
       </c>
       <c r="L4" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="M4" s="200" t="s">
+      <c r="M4" s="204" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="209" t="s">
+      <c r="N4" s="196" t="s">
         <v>38</v>
       </c>
       <c r="Q4" s="45"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="203"/>
-      <c r="B5" s="203"/>
-      <c r="C5" s="211"/>
-      <c r="D5" s="203"/>
-      <c r="E5" s="199"/>
-      <c r="F5" s="203"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="199"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="199"/>
-      <c r="K5" s="208"/>
+      <c r="A5" s="200"/>
+      <c r="B5" s="200"/>
+      <c r="C5" s="199"/>
+      <c r="D5" s="200"/>
+      <c r="E5" s="203"/>
+      <c r="F5" s="200"/>
+      <c r="G5" s="207"/>
+      <c r="H5" s="203"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="203"/>
+      <c r="K5" s="210"/>
       <c r="L5" s="63" t="str">
         <f>RESUMEN!B8</f>
-        <v>VTO 15/09</v>
-      </c>
-      <c r="M5" s="201"/>
-      <c r="N5" s="210"/>
+        <v>VTO 15/10</v>
+      </c>
+      <c r="M5" s="205"/>
+      <c r="N5" s="197"/>
     </row>
     <row r="6" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="66">
@@ -3036,11 +3062,11 @@
         <v>6.69</v>
       </c>
       <c r="E6" s="76">
-        <v>213152.01</v>
+        <v>239912.01</v>
       </c>
       <c r="F6" s="78">
         <f>E6</f>
-        <v>213152.01</v>
+        <v>239912.01</v>
       </c>
       <c r="G6" s="79">
         <f t="shared" ref="G6:G23" si="0">E6-F6</f>
@@ -3055,7 +3081,7 @@
       </c>
       <c r="J6" s="81">
         <f>L$2*D6/100</f>
-        <v>234150</v>
+        <v>252498.60747300004</v>
       </c>
       <c r="K6" s="168">
         <f t="shared" ref="K6:K23" si="1">F$2*D6/100</f>
@@ -3063,15 +3089,15 @@
       </c>
       <c r="L6" s="83">
         <f>ROUND(SUM(G6:K6),0) + O6</f>
-        <v>239912.01</v>
+        <v>258261.01</v>
       </c>
       <c r="M6" s="84">
         <f>ROUND(L6*6% + L6,0) + O6</f>
-        <v>254307.01</v>
+        <v>273757.01</v>
       </c>
       <c r="N6" s="85">
         <f>ROUND(L6*3%,0) + L6</f>
-        <v>247109.01</v>
+        <v>266009.01</v>
       </c>
       <c r="O6" s="45">
         <v>0.01</v>
@@ -3090,26 +3116,26 @@
         <v>5.88</v>
       </c>
       <c r="E7" s="76">
-        <v>365762.02</v>
+        <v>330100.02</v>
       </c>
       <c r="F7" s="78">
-        <f>150000+100000</f>
-        <v>250000</v>
+        <f>100000</f>
+        <v>100000</v>
       </c>
       <c r="G7" s="79">
         <f t="shared" si="0"/>
-        <v>115762.02000000002</v>
+        <v>230100.02000000002</v>
       </c>
       <c r="H7" s="79">
         <f t="shared" ref="H7:H23" si="2">IF(G7&gt;0,G7*3%,0)</f>
-        <v>3472.8606000000004</v>
+        <v>6903.0006000000003</v>
       </c>
       <c r="I7" s="80">
         <v>0</v>
       </c>
       <c r="J7" s="81">
         <f t="shared" ref="J7:J23" si="3">L$2*D7%</f>
-        <v>205800</v>
+        <v>221927.02719600001</v>
       </c>
       <c r="K7" s="168">
         <f t="shared" si="1"/>
@@ -3117,15 +3143,15 @@
       </c>
       <c r="L7" s="83">
         <f t="shared" ref="L7:L23" si="4">ROUND(SUM(G7:K7),0) + O7</f>
-        <v>330100.02</v>
+        <v>463995.02</v>
       </c>
       <c r="M7" s="84">
         <f t="shared" ref="M7:M23" si="5">ROUND(L7*6% + L7,0) + O7</f>
-        <v>349906.02</v>
+        <v>491835.02</v>
       </c>
       <c r="N7" s="85">
         <f t="shared" ref="N7:N23" si="6">ROUND(L7*3%,0) + L7</f>
-        <v>340003.02</v>
+        <v>477915.02</v>
       </c>
       <c r="O7" s="45">
         <f>O6+0.01</f>
@@ -3146,11 +3172,11 @@
         <v>6.65</v>
       </c>
       <c r="E8" s="76">
-        <v>211878.03</v>
+        <v>238478.03</v>
       </c>
       <c r="F8" s="78">
         <f>E8</f>
-        <v>211878.03</v>
+        <v>238478.03</v>
       </c>
       <c r="G8" s="79">
         <f t="shared" si="0"/>
@@ -3165,7 +3191,7 @@
       </c>
       <c r="J8" s="81">
         <f t="shared" si="3"/>
-        <v>232750</v>
+        <v>250988.89980500005</v>
       </c>
       <c r="K8" s="168">
         <f t="shared" si="1"/>
@@ -3173,15 +3199,15 @@
       </c>
       <c r="L8" s="83">
         <f t="shared" si="4"/>
-        <v>238478.03</v>
+        <v>256717.03</v>
       </c>
       <c r="M8" s="84">
         <f t="shared" si="5"/>
-        <v>252787.03</v>
+        <v>272120.03000000003</v>
       </c>
       <c r="N8" s="85">
         <f t="shared" si="6"/>
-        <v>245632.03</v>
+        <v>264419.03000000003</v>
       </c>
       <c r="O8" s="45">
         <f t="shared" ref="O8:O24" si="8">O7+0.01</f>
@@ -3201,11 +3227,11 @@
         <v>6.73</v>
       </c>
       <c r="E9" s="76">
-        <v>214427.04</v>
+        <v>241347.04</v>
       </c>
       <c r="F9" s="78">
         <f t="shared" ref="F9:F23" si="9">E9</f>
-        <v>214427.04</v>
+        <v>241347.04</v>
       </c>
       <c r="G9" s="79">
         <f t="shared" si="0"/>
@@ -3220,7 +3246,7 @@
       </c>
       <c r="J9" s="81">
         <f t="shared" si="3"/>
-        <v>235550</v>
+        <v>254008.31514100003</v>
       </c>
       <c r="K9" s="168">
         <f t="shared" si="1"/>
@@ -3228,15 +3254,15 @@
       </c>
       <c r="L9" s="83">
         <f t="shared" si="4"/>
-        <v>241347.04</v>
+        <v>259805.04</v>
       </c>
       <c r="M9" s="84">
         <f t="shared" si="5"/>
-        <v>255828.04</v>
+        <v>275393.03999999998</v>
       </c>
       <c r="N9" s="85">
         <f t="shared" si="6"/>
-        <v>248587.04</v>
+        <v>267599.04000000004</v>
       </c>
       <c r="O9" s="45">
         <f t="shared" si="8"/>
@@ -3257,26 +3283,23 @@
         <v>8.0399999999999991</v>
       </c>
       <c r="E10" s="76">
-        <v>263850.05</v>
-      </c>
-      <c r="F10" s="78">
-        <f>E10</f>
-        <v>263850.05</v>
-      </c>
+        <v>288325.05</v>
+      </c>
+      <c r="F10" s="78"/>
       <c r="G10" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>288325.05</v>
       </c>
       <c r="H10" s="79">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8649.7514999999985</v>
       </c>
       <c r="I10" s="80">
         <v>0</v>
       </c>
       <c r="J10" s="81">
         <f t="shared" si="3"/>
-        <v>281399.99999999994</v>
+        <v>303451.24126799998</v>
       </c>
       <c r="K10" s="168">
         <f t="shared" si="1"/>
@@ -3284,15 +3307,15 @@
       </c>
       <c r="L10" s="83">
         <f t="shared" si="4"/>
-        <v>288325.05</v>
+        <v>607351.05000000005</v>
       </c>
       <c r="M10" s="84">
         <f t="shared" si="5"/>
-        <v>305625.05</v>
+        <v>643792.05000000005</v>
       </c>
       <c r="N10" s="85">
         <f t="shared" si="6"/>
-        <v>296975.05</v>
+        <v>625572.05000000005</v>
       </c>
       <c r="O10" s="45">
         <f t="shared" si="8"/>
@@ -3313,11 +3336,11 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="E11" s="76">
-        <v>150704.06</v>
+        <v>169624.06</v>
       </c>
       <c r="F11" s="78">
         <f t="shared" si="9"/>
-        <v>150704.06</v>
+        <v>169624.06</v>
       </c>
       <c r="G11" s="79">
         <f t="shared" si="0"/>
@@ -3332,7 +3355,7 @@
       </c>
       <c r="J11" s="81">
         <f t="shared" si="3"/>
-        <v>165550</v>
+        <v>178522.93174100004</v>
       </c>
       <c r="K11" s="168">
         <f t="shared" si="1"/>
@@ -3340,15 +3363,15 @@
       </c>
       <c r="L11" s="83">
         <f t="shared" si="4"/>
-        <v>169624.06</v>
+        <v>182597.06</v>
       </c>
       <c r="M11" s="84">
         <f t="shared" si="5"/>
-        <v>179802.06</v>
+        <v>193553.06</v>
       </c>
       <c r="N11" s="85">
         <f t="shared" si="6"/>
-        <v>174713.06</v>
+        <v>188075.06</v>
       </c>
       <c r="O11" s="45">
         <f t="shared" si="8"/>
@@ -3368,11 +3391,11 @@
         <v>5.67</v>
       </c>
       <c r="E12" s="76">
-        <v>180654.07</v>
+        <v>203334.07</v>
       </c>
       <c r="F12" s="78">
         <f>E12</f>
-        <v>180654.07</v>
+        <v>203334.07</v>
       </c>
       <c r="G12" s="79">
         <f t="shared" si="0"/>
@@ -3387,7 +3410,7 @@
       </c>
       <c r="J12" s="81">
         <f t="shared" si="3"/>
-        <v>198450</v>
+        <v>214001.06193900004</v>
       </c>
       <c r="K12" s="168">
         <f t="shared" si="1"/>
@@ -3395,15 +3418,15 @@
       </c>
       <c r="L12" s="83">
         <f t="shared" si="4"/>
-        <v>203334.07</v>
+        <v>218885.07</v>
       </c>
       <c r="M12" s="84">
         <f t="shared" si="5"/>
-        <v>215534.07</v>
+        <v>232018.07</v>
       </c>
       <c r="N12" s="85">
         <f t="shared" si="6"/>
-        <v>209434.07</v>
+        <v>225452.07</v>
       </c>
       <c r="O12" s="45">
         <f t="shared" si="8"/>
@@ -3423,26 +3446,26 @@
         <v>5.67</v>
       </c>
       <c r="E13" s="76">
-        <v>180654.07999999999</v>
+        <v>204008.08</v>
       </c>
       <c r="F13" s="78">
-        <f>100000+80000</f>
-        <v>180000</v>
+        <f>104000</f>
+        <v>104000</v>
       </c>
       <c r="G13" s="79">
         <f t="shared" si="0"/>
-        <v>654.07999999998719</v>
+        <v>100008.07999999999</v>
       </c>
       <c r="H13" s="79">
         <f t="shared" si="2"/>
-        <v>19.622399999999615</v>
+        <v>3000.2423999999996</v>
       </c>
       <c r="I13" s="80">
         <v>0</v>
       </c>
       <c r="J13" s="81">
         <f t="shared" si="3"/>
-        <v>198450</v>
+        <v>214001.06193900004</v>
       </c>
       <c r="K13" s="168">
         <f t="shared" si="1"/>
@@ -3450,15 +3473,15 @@
       </c>
       <c r="L13" s="83">
         <f t="shared" si="4"/>
-        <v>204008.08</v>
+        <v>321893.08</v>
       </c>
       <c r="M13" s="84">
         <f t="shared" si="5"/>
-        <v>216249.08</v>
+        <v>341207.08</v>
       </c>
       <c r="N13" s="85">
         <f t="shared" si="6"/>
-        <v>210128.08</v>
+        <v>331550.08000000002</v>
       </c>
       <c r="O13" s="45">
         <f t="shared" si="8"/>
@@ -3481,11 +3504,11 @@
         <v>7.67</v>
       </c>
       <c r="E14" s="76">
-        <v>244377.09</v>
+        <v>275057.09000000003</v>
       </c>
       <c r="F14" s="78">
         <f t="shared" si="9"/>
-        <v>244377.09</v>
+        <v>275057.09000000003</v>
       </c>
       <c r="G14" s="79">
         <f t="shared" si="0"/>
@@ -3500,7 +3523,7 @@
       </c>
       <c r="J14" s="81">
         <f t="shared" si="3"/>
-        <v>268450</v>
+        <v>289486.44533900003</v>
       </c>
       <c r="K14" s="168">
         <f t="shared" si="1"/>
@@ -3508,15 +3531,15 @@
       </c>
       <c r="L14" s="83">
         <f t="shared" si="4"/>
-        <v>275057.09000000003</v>
+        <v>296093.09000000003</v>
       </c>
       <c r="M14" s="84">
         <f t="shared" si="5"/>
-        <v>291561.09000000003</v>
+        <v>313859.09000000003</v>
       </c>
       <c r="N14" s="85">
         <f t="shared" si="6"/>
-        <v>283309.09000000003</v>
+        <v>304976.09000000003</v>
       </c>
       <c r="O14" s="45">
         <f t="shared" si="8"/>
@@ -3536,25 +3559,26 @@
         <v>4.9000000000000004</v>
       </c>
       <c r="E15" s="76">
-        <v>160805.1</v>
+        <v>185695.1</v>
       </c>
       <c r="F15" s="78">
-        <v>151121.1</v>
+        <f>E15</f>
+        <v>185695.1</v>
       </c>
       <c r="G15" s="79">
         <f t="shared" si="0"/>
-        <v>9684</v>
+        <v>0</v>
       </c>
       <c r="H15" s="79">
         <f t="shared" si="2"/>
-        <v>290.52</v>
+        <v>0</v>
       </c>
       <c r="I15" s="80">
         <v>0</v>
       </c>
       <c r="J15" s="81">
         <f t="shared" si="3"/>
-        <v>171500</v>
+        <v>184939.18933000002</v>
       </c>
       <c r="K15" s="168">
         <f t="shared" si="1"/>
@@ -3562,15 +3586,15 @@
       </c>
       <c r="L15" s="83">
         <f t="shared" si="4"/>
-        <v>185695.1</v>
+        <v>189160.1</v>
       </c>
       <c r="M15" s="84">
         <f t="shared" si="5"/>
-        <v>196837.1</v>
+        <v>200510.1</v>
       </c>
       <c r="N15" s="85">
         <f t="shared" si="6"/>
-        <v>191266.1</v>
+        <v>194835.1</v>
       </c>
       <c r="O15" s="45">
         <f t="shared" si="8"/>
@@ -3590,11 +3614,11 @@
         <v>5.63</v>
       </c>
       <c r="E16" s="76">
-        <v>179379.11</v>
+        <v>201899.11</v>
       </c>
       <c r="F16" s="78">
         <f t="shared" si="9"/>
-        <v>179379.11</v>
+        <v>201899.11</v>
       </c>
       <c r="G16" s="79">
         <f t="shared" si="0"/>
@@ -3609,7 +3633,7 @@
       </c>
       <c r="J16" s="81">
         <f t="shared" si="3"/>
-        <v>197050</v>
+        <v>212491.35427100002</v>
       </c>
       <c r="K16" s="168">
         <f t="shared" si="1"/>
@@ -3617,15 +3641,15 @@
       </c>
       <c r="L16" s="83">
         <f t="shared" si="4"/>
-        <v>201899.11</v>
+        <v>217341.11</v>
       </c>
       <c r="M16" s="84">
         <f t="shared" si="5"/>
-        <v>214013.11</v>
+        <v>230382.11</v>
       </c>
       <c r="N16" s="85">
         <f t="shared" si="6"/>
-        <v>207956.11</v>
+        <v>223861.11</v>
       </c>
       <c r="O16" s="45">
         <f t="shared" si="8"/>
@@ -3645,11 +3669,11 @@
         <v>5.55</v>
       </c>
       <c r="E17" s="76">
-        <v>176830.12</v>
+        <v>199030.12</v>
       </c>
       <c r="F17" s="78">
         <f t="shared" si="9"/>
-        <v>176830.12</v>
+        <v>199030.12</v>
       </c>
       <c r="G17" s="79">
         <f t="shared" si="0"/>
@@ -3664,7 +3688,7 @@
       </c>
       <c r="J17" s="81">
         <f t="shared" si="3"/>
-        <v>194250</v>
+        <v>209471.93893500001</v>
       </c>
       <c r="K17" s="168">
         <f t="shared" si="1"/>
@@ -3672,15 +3696,15 @@
       </c>
       <c r="L17" s="83">
         <f t="shared" si="4"/>
-        <v>199030.12</v>
+        <v>214252.12</v>
       </c>
       <c r="M17" s="84">
         <f t="shared" si="5"/>
-        <v>210972.12</v>
+        <v>227107.12</v>
       </c>
       <c r="N17" s="85">
         <f t="shared" si="6"/>
-        <v>205001.12</v>
+        <v>220680.12</v>
       </c>
       <c r="O17" s="45">
         <f t="shared" si="8"/>
@@ -3700,11 +3724,11 @@
         <v>11.06</v>
       </c>
       <c r="E18" s="76">
-        <v>352386.13</v>
+        <v>396626.13</v>
       </c>
       <c r="F18" s="78">
         <f>E18</f>
-        <v>352386.13</v>
+        <v>396626.13</v>
       </c>
       <c r="G18" s="79">
         <f t="shared" si="0"/>
@@ -3719,7 +3743,7 @@
       </c>
       <c r="J18" s="81">
         <f t="shared" si="3"/>
-        <v>387100</v>
+        <v>417434.17020200007</v>
       </c>
       <c r="K18" s="168">
         <f t="shared" si="1"/>
@@ -3727,15 +3751,15 @@
       </c>
       <c r="L18" s="83">
         <f t="shared" si="4"/>
-        <v>396626.13</v>
+        <v>426961.13</v>
       </c>
       <c r="M18" s="84">
         <f t="shared" si="5"/>
-        <v>420424.13</v>
+        <v>452579.13</v>
       </c>
       <c r="N18" s="85">
         <f t="shared" si="6"/>
-        <v>408525.13</v>
+        <v>439770.13</v>
       </c>
       <c r="O18" s="45">
         <f t="shared" si="8"/>
@@ -3755,23 +3779,23 @@
         <v>3.3</v>
       </c>
       <c r="E19" s="76">
-        <v>95562.14</v>
+        <v>216771.14</v>
       </c>
       <c r="F19" s="78"/>
       <c r="G19" s="79">
         <f t="shared" si="0"/>
-        <v>95562.14</v>
+        <v>216771.14</v>
       </c>
       <c r="H19" s="79">
         <f t="shared" si="2"/>
-        <v>2866.8642</v>
+        <v>6503.1342000000004</v>
       </c>
       <c r="I19" s="80">
         <v>0</v>
       </c>
       <c r="J19" s="81">
         <f t="shared" si="3"/>
-        <v>115500</v>
+        <v>124550.88261000002</v>
       </c>
       <c r="K19" s="168">
         <f t="shared" si="1"/>
@@ -3779,15 +3803,15 @@
       </c>
       <c r="L19" s="83">
         <f t="shared" si="4"/>
-        <v>216771.14</v>
+        <v>350668.14</v>
       </c>
       <c r="M19" s="84">
         <f t="shared" si="5"/>
-        <v>229777.14</v>
+        <v>371708.14</v>
       </c>
       <c r="N19" s="85">
         <f t="shared" si="6"/>
-        <v>223274.14</v>
+        <v>361188.14</v>
       </c>
       <c r="O19" s="45">
         <f t="shared" si="8"/>
@@ -3807,11 +3831,11 @@
         <v>1.8</v>
       </c>
       <c r="E20" s="76">
-        <v>57350.15</v>
+        <v>64550.15</v>
       </c>
       <c r="F20" s="78">
         <f>E20</f>
-        <v>57350.15</v>
+        <v>64550.15</v>
       </c>
       <c r="G20" s="79">
         <f t="shared" si="0"/>
@@ -3826,7 +3850,7 @@
       </c>
       <c r="J20" s="81">
         <f t="shared" si="3"/>
-        <v>63000.000000000007</v>
+        <v>67936.845060000021</v>
       </c>
       <c r="K20" s="168">
         <f t="shared" si="1"/>
@@ -3834,15 +3858,15 @@
       </c>
       <c r="L20" s="83">
         <f t="shared" si="4"/>
-        <v>64550.15</v>
+        <v>69487.149999999994</v>
       </c>
       <c r="M20" s="84">
         <f t="shared" si="5"/>
-        <v>68423.149999999994</v>
+        <v>73656.149999999994</v>
       </c>
       <c r="N20" s="85">
         <f t="shared" si="6"/>
-        <v>66487.149999999994</v>
+        <v>71572.149999999994</v>
       </c>
       <c r="O20" s="45">
         <f t="shared" si="8"/>
@@ -3862,11 +3886,11 @@
         <v>3.22</v>
       </c>
       <c r="E21" s="76">
-        <v>102594.16</v>
+        <v>115474.16</v>
       </c>
       <c r="F21" s="78">
         <f>E21</f>
-        <v>102594.16</v>
+        <v>115474.16</v>
       </c>
       <c r="G21" s="79">
         <f t="shared" si="0"/>
@@ -3881,7 +3905,7 @@
       </c>
       <c r="J21" s="81">
         <f t="shared" si="3"/>
-        <v>112700</v>
+        <v>121531.46727400001</v>
       </c>
       <c r="K21" s="168">
         <f t="shared" si="1"/>
@@ -3889,15 +3913,15 @@
       </c>
       <c r="L21" s="83">
         <f t="shared" si="4"/>
-        <v>115474.16</v>
+        <v>124305.16</v>
       </c>
       <c r="M21" s="84">
         <f t="shared" si="5"/>
-        <v>122403.16</v>
+        <v>131763.16</v>
       </c>
       <c r="N21" s="85">
         <f t="shared" si="6"/>
-        <v>118938.16</v>
+        <v>128034.16</v>
       </c>
       <c r="O21" s="45">
         <f t="shared" si="8"/>
@@ -3918,23 +3942,23 @@
         <v>2.61</v>
       </c>
       <c r="E22" s="77">
-        <v>83158.17</v>
+        <v>179251.17</v>
       </c>
       <c r="F22" s="78"/>
       <c r="G22" s="79">
         <f t="shared" si="0"/>
-        <v>83158.17</v>
+        <v>179251.17</v>
       </c>
       <c r="H22" s="79">
         <f t="shared" si="2"/>
-        <v>2494.7450999999996</v>
+        <v>5377.5351000000001</v>
       </c>
       <c r="I22" s="80">
         <v>0</v>
       </c>
       <c r="J22" s="81">
         <f t="shared" si="3"/>
-        <v>91350</v>
+        <v>98508.425337000008</v>
       </c>
       <c r="K22" s="168">
         <f t="shared" si="1"/>
@@ -3942,15 +3966,15 @@
       </c>
       <c r="L22" s="83">
         <f t="shared" si="4"/>
-        <v>179251.17</v>
+        <v>285385.17</v>
       </c>
       <c r="M22" s="84">
         <f t="shared" si="5"/>
-        <v>190006.17</v>
+        <v>302508.17</v>
       </c>
       <c r="N22" s="85">
         <f t="shared" si="6"/>
-        <v>184629.17</v>
+        <v>293947.17</v>
       </c>
       <c r="O22" s="45">
         <f t="shared" si="8"/>
@@ -3970,11 +3994,11 @@
         <v>4.28</v>
       </c>
       <c r="E23" s="76">
-        <v>136367.18</v>
+        <v>153487.18</v>
       </c>
       <c r="F23" s="78">
         <f t="shared" si="9"/>
-        <v>136367.18</v>
+        <v>153487.18</v>
       </c>
       <c r="G23" s="79">
         <f t="shared" si="0"/>
@@ -3989,7 +4013,7 @@
       </c>
       <c r="J23" s="81">
         <f t="shared" si="3"/>
-        <v>149800.00000000003</v>
+        <v>161538.72047600005</v>
       </c>
       <c r="K23" s="168">
         <f t="shared" si="1"/>
@@ -3997,15 +4021,15 @@
       </c>
       <c r="L23" s="83">
         <f t="shared" si="4"/>
-        <v>153487.18</v>
+        <v>165225.18</v>
       </c>
       <c r="M23" s="84">
         <f t="shared" si="5"/>
-        <v>162696.18</v>
+        <v>175139.18</v>
       </c>
       <c r="N23" s="85">
         <f t="shared" si="6"/>
-        <v>158092.18</v>
+        <v>170182.18</v>
       </c>
       <c r="O23" s="45">
         <f t="shared" si="8"/>
@@ -4110,19 +4134,19 @@
       </c>
       <c r="E29" s="55">
         <f>SUM(E6:E28)</f>
-        <v>3369890.7100000004</v>
+        <v>3902969.7100000004</v>
       </c>
       <c r="F29" s="64">
         <f>SUM(F6:F28)</f>
-        <v>3065070.3000000007</v>
+        <v>2888514.2500000005</v>
       </c>
       <c r="G29" s="64">
         <f>SUM(G6:G28)</f>
-        <v>304820.40999999997</v>
+        <v>1014455.4600000001</v>
       </c>
       <c r="H29" s="64">
         <f t="shared" ref="H29:M29" si="10">SUM(H6:H28)</f>
-        <v>9144.6123000000007</v>
+        <v>30433.663799999998</v>
       </c>
       <c r="I29" s="64">
         <f t="shared" si="10"/>
@@ -4130,7 +4154,7 @@
       </c>
       <c r="J29" s="137">
         <f t="shared" si="10"/>
-        <v>3502800</v>
+        <v>3777288.5853360011</v>
       </c>
       <c r="K29" s="64">
         <f t="shared" si="10"/>
@@ -4138,15 +4162,15 @@
       </c>
       <c r="L29" s="100">
         <f>SUM(L6:L23)</f>
-        <v>3902969.7100000004</v>
+        <v>4908382.71</v>
       </c>
       <c r="M29" s="100">
         <f t="shared" si="10"/>
-        <v>4137151.7100000004</v>
+        <v>5202887.71</v>
       </c>
       <c r="N29" s="100">
         <f>SUM(N6:N28)</f>
-        <v>4020059.7100000004</v>
+        <v>5055637.71</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4155,94 +4179,88 @@
     </row>
     <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:17" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="195" t="str">
+      <c r="B32" s="186" t="str">
         <f>RESUMEN!A13</f>
         <v>ESTIMADOS PROPIETARIOS E INQUILINOS: POR FAVOR LOS QUE ABONAN EN PRIMER VENCIMIENTO ABONEN EL MONTO DE PRIMER VENCIMIENTO, ASI AGILIZAN LA LIQUIDACION, RESPETEN LOS CENTAVOS CORRESPONDIENTES A LA UNIDAD FUNCIONAL. ES DE CARÁCTER OBLIGATORIO INFORMAR VIA MAIL LAS EXPENSAS. CASO CONTRARIO SE INFORMARA VIA CARTA DOCUMENTO A LA UNIDAD FUNCIONAL QUE CREEMOS QUE CORRESPONDE, CUYO COSTO SERA IMPUTADO A LA UNIDAD FUNCIONAL SOSPECHADA.</v>
       </c>
-      <c r="C32" s="195"/>
-      <c r="D32" s="195"/>
-      <c r="E32" s="195"/>
-      <c r="F32" s="195"/>
-      <c r="G32" s="195"/>
-      <c r="H32" s="195"/>
-      <c r="I32" s="195"/>
-      <c r="J32" s="195"/>
-      <c r="K32" s="195"/>
-      <c r="L32" s="195"/>
+      <c r="C32" s="186"/>
+      <c r="D32" s="186"/>
+      <c r="E32" s="186"/>
+      <c r="F32" s="186"/>
+      <c r="G32" s="186"/>
+      <c r="H32" s="186"/>
+      <c r="I32" s="186"/>
+      <c r="J32" s="186"/>
+      <c r="K32" s="186"/>
+      <c r="L32" s="186"/>
     </row>
     <row r="33" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="195"/>
-      <c r="C33" s="195"/>
-      <c r="D33" s="195"/>
-      <c r="E33" s="195"/>
-      <c r="F33" s="195"/>
-      <c r="G33" s="195"/>
-      <c r="H33" s="195"/>
-      <c r="I33" s="195"/>
-      <c r="J33" s="195"/>
-      <c r="K33" s="195"/>
-      <c r="L33" s="195"/>
+      <c r="B33" s="186"/>
+      <c r="C33" s="186"/>
+      <c r="D33" s="186"/>
+      <c r="E33" s="186"/>
+      <c r="F33" s="186"/>
+      <c r="G33" s="186"/>
+      <c r="H33" s="186"/>
+      <c r="I33" s="186"/>
+      <c r="J33" s="186"/>
+      <c r="K33" s="186"/>
+      <c r="L33" s="186"/>
     </row>
     <row r="34" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="195"/>
-      <c r="C34" s="195"/>
-      <c r="D34" s="195"/>
-      <c r="E34" s="195"/>
-      <c r="F34" s="195"/>
-      <c r="G34" s="195"/>
-      <c r="H34" s="195"/>
-      <c r="I34" s="195"/>
-      <c r="J34" s="195"/>
-      <c r="K34" s="195"/>
-      <c r="L34" s="195"/>
+      <c r="B34" s="186"/>
+      <c r="C34" s="186"/>
+      <c r="D34" s="186"/>
+      <c r="E34" s="186"/>
+      <c r="F34" s="186"/>
+      <c r="G34" s="186"/>
+      <c r="H34" s="186"/>
+      <c r="I34" s="186"/>
+      <c r="J34" s="186"/>
+      <c r="K34" s="186"/>
+      <c r="L34" s="186"/>
     </row>
     <row r="35" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="195"/>
-      <c r="C35" s="195"/>
-      <c r="D35" s="195"/>
-      <c r="E35" s="195"/>
-      <c r="F35" s="195"/>
-      <c r="G35" s="195"/>
-      <c r="H35" s="195"/>
-      <c r="I35" s="195"/>
-      <c r="J35" s="195"/>
-      <c r="K35" s="195"/>
-      <c r="L35" s="195"/>
+      <c r="B35" s="186"/>
+      <c r="C35" s="186"/>
+      <c r="D35" s="186"/>
+      <c r="E35" s="186"/>
+      <c r="F35" s="186"/>
+      <c r="G35" s="186"/>
+      <c r="H35" s="186"/>
+      <c r="I35" s="186"/>
+      <c r="J35" s="186"/>
+      <c r="K35" s="186"/>
+      <c r="L35" s="186"/>
     </row>
     <row r="36" spans="2:12" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="195"/>
-      <c r="C36" s="195"/>
-      <c r="D36" s="195"/>
-      <c r="E36" s="195"/>
-      <c r="F36" s="195"/>
-      <c r="G36" s="195"/>
-      <c r="H36" s="195"/>
-      <c r="I36" s="195"/>
-      <c r="J36" s="195"/>
-      <c r="K36" s="195"/>
-      <c r="L36" s="195"/>
+      <c r="B36" s="186"/>
+      <c r="C36" s="186"/>
+      <c r="D36" s="186"/>
+      <c r="E36" s="186"/>
+      <c r="F36" s="186"/>
+      <c r="G36" s="186"/>
+      <c r="H36" s="186"/>
+      <c r="I36" s="186"/>
+      <c r="J36" s="186"/>
+      <c r="K36" s="186"/>
+      <c r="L36" s="186"/>
     </row>
     <row r="37" spans="2:12" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="195"/>
-      <c r="C37" s="195"/>
-      <c r="D37" s="195"/>
-      <c r="E37" s="195"/>
-      <c r="F37" s="195"/>
-      <c r="G37" s="195"/>
-      <c r="H37" s="195"/>
-      <c r="I37" s="195"/>
-      <c r="J37" s="195"/>
-      <c r="K37" s="195"/>
-      <c r="L37" s="195"/>
+      <c r="B37" s="186"/>
+      <c r="C37" s="186"/>
+      <c r="D37" s="186"/>
+      <c r="E37" s="186"/>
+      <c r="F37" s="186"/>
+      <c r="G37" s="186"/>
+      <c r="H37" s="186"/>
+      <c r="I37" s="186"/>
+      <c r="J37" s="186"/>
+      <c r="K37" s="186"/>
+      <c r="L37" s="186"/>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="B32:L37"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
     <mergeCell ref="D1:L1"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="E4:E5"/>
@@ -4252,6 +4270,12 @@
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="B32:L37"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
